--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N59_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>12.87023758492247</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1.237773422644613</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.137059326296587</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -497,6 +497,38 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W0066F0001T0006Z000C1N59.png</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10.4484433435137</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.59611893232929</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.237773422644613</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.137059326296587</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.92399018880292</v>
+        <v>2.100148405680475</v>
       </c>
       <c r="D2" t="n">
-        <v>12.87023758492247</v>
+        <v>2.091413607549901</v>
       </c>
       <c r="E2" t="n">
-        <v>1.237773422644613</v>
+        <v>0.2011381811797498</v>
       </c>
       <c r="F2" t="n">
-        <v>1.137059326296587</v>
+        <v>0.1847721405231952</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4484433435137</v>
+        <v>1.697872043320976</v>
       </c>
       <c r="D3" t="n">
-        <v>10.59611893232929</v>
+        <v>1.72186932650351</v>
       </c>
       <c r="E3" t="n">
-        <v>1.237773422644613</v>
+        <v>0.2011381811797498</v>
       </c>
       <c r="F3" t="n">
-        <v>1.137059326296587</v>
+        <v>0.1847721405231952</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
